--- a/outputs/daily/hr_rankings_2026-08-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08.xlsx
@@ -10254,34 +10254,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23278,34 +23274,30 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39602,34 +39594,30 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47082,34 +47070,30 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -47366,34 +47350,30 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48202,34 +48182,30 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48486,34 +48462,30 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -55686,34 +55658,30 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -71372,28 +71340,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W257" t="inlineStr"/>
-      <c r="X257" t="inlineStr"/>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y257" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB257" t="inlineStr"/>
       <c r="AC257" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08.xlsx
@@ -1386,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1670,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1954,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3086,34 +3074,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3650,34 +3634,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4683,47 +4663,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>682848</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Endy Rodríguez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-08T19:05:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4732,7 +4712,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4746,26 +4726,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>48.7</v>
+        <v>39.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>82.7</v>
+        <v>67.8</v>
       </c>
       <c r="S16" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>48.3</v>
+        <v>62.4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4779,7 +4759,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4800,7 +4780,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4817,142 +4797,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>90.76</t>
+          <t>92.34</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.4691</t>
+          <t>100.3363</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4786</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1921</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3416</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>46.21</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>33.36</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1922</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4963,27 +4943,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>682848</t>
+          <t>646240</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Endy Rodríguez</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4993,17 +4973,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5012,7 +4992,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5026,26 +5006,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>39.9</v>
+        <v>58.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>75.09999999999999</v>
+        <v>47.4</v>
       </c>
       <c r="R17" t="n">
-        <v>67.8</v>
+        <v>53.3</v>
       </c>
       <c r="S17" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>62.4</v>
+        <v>56.2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5054,37 +5034,33 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5101,7 +5077,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -5121,122 +5097,122 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>52.74</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>92.34</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.3363</t>
+          <t>103.133</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.2231</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.2291</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5247,27 +5223,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>646240</t>
+          <t>701398</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T22:45:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5277,26 +5253,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jackson Jobe</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>61.8</v>
+        <v>61.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5310,26 +5286,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>58.1</v>
+        <v>61.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>47.4</v>
+        <v>22</v>
       </c>
       <c r="R18" t="n">
-        <v>53.3</v>
+        <v>71.7</v>
       </c>
       <c r="S18" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>56.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5343,7 +5319,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5364,7 +5340,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5381,142 +5357,142 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.4% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>52.74</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>103.133</t>
+          <t>101.6267</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.5201</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.2231</t>
+          <t>0.2589</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.2291</t>
+          <t>0.2438</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>0.3486</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1025</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5527,56 +5503,56 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>701398</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-08T22:45:00Z</t>
+          <t>2026-08-08T19:05:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,26 +5566,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>61.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>46.3</v>
       </c>
       <c r="R19" t="n">
-        <v>71.7</v>
+        <v>82.7</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>77.40000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5623,7 +5599,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5644,7 +5620,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5661,127 +5637,127 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.4% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>90.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.6267</t>
+          <t>103.4691</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.5201</t>
+          <t>0.4786</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2589</t>
+          <t>0.1921</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.3416</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2438</t>
+          <t>0.1922</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3486</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1025</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -5796,7 +5772,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -8146,34 +8122,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9266,34 +9238,30 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9826,34 +9794,30 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10985,12 +10949,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -11000,7 +10964,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -11222,34 +11186,30 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12065,7 +12025,7 @@
         <v>50</v>
       </c>
       <c r="U42" t="n">
-        <v>77.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -12117,12 +12077,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -12918,34 +12878,30 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13720,7 +13676,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13753,7 +13709,7 @@
         <v>78</v>
       </c>
       <c r="U48" t="n">
-        <v>13.3</v>
+        <v>10.6</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13805,12 +13761,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13820,7 +13776,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -14042,34 +13998,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14326,34 +14278,30 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14890,34 +14838,30 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16562,34 +16506,30 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17130,34 +17070,30 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18534,34 +18470,30 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -19098,34 +19030,30 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -19382,34 +19310,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19666,34 +19590,30 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -22182,34 +22102,30 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23882,34 +23798,30 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25002,34 +24914,30 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26114,34 +26022,30 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -27711,52 +27615,52 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>502671</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Paul Goldschmidt</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-09T01:50:00Z</t>
+          <t>2026-08-08T19:05:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -27774,62 +27678,58 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>54.6</v>
+        <v>36</v>
       </c>
       <c r="Q98" t="n">
-        <v>41.6</v>
+        <v>21</v>
       </c>
       <c r="R98" t="n">
-        <v>25.4</v>
+        <v>82.7</v>
       </c>
       <c r="S98" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T98" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U98" t="n">
-        <v>19.1</v>
+        <v>3.4</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27849,134 +27749,142 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 1 HR</t>
+          <t>Last 7 games: 2/14, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 11.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>100.6066</t>
+          <t>99.3313</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.4245</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.2299</t>
+          <t>0.1777</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3115</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>53.09</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>53.73</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>29.28</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.1822</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1555</t>
+          <t>0.1087</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>23.72</t>
-        </is>
-      </c>
-      <c r="BG98" t="inlineStr"/>
-      <c r="BH98" t="inlineStr"/>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="BG98" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH98" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27987,47 +27895,47 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-08T19:05:00Z</t>
+          <t>2026-08-09T01:50:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -28036,7 +27944,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -28050,61 +27958,65 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>17</v>
+        <v>54.6</v>
       </c>
       <c r="Q99" t="n">
-        <v>45.1</v>
+        <v>41.6</v>
       </c>
       <c r="R99" t="n">
-        <v>82.7</v>
+        <v>25.4</v>
       </c>
       <c r="S99" t="n">
-        <v>86.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T99" t="n">
         <v>75</v>
       </c>
       <c r="U99" t="n">
-        <v>34.4</v>
+        <v>19.1</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -28121,12 +28033,12 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -28136,127 +28048,119 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 3/24, 1 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>96.7879</t>
+          <t>100.6066</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.3625</t>
+          <t>0.4245</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.2299</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>68.93</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>53.09</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>53.73</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>41.59</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.1593</t>
+          <t>0.2041</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1555</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>32.8</t>
-        </is>
-      </c>
-      <c r="BG99" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH99" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t>23.72</t>
+        </is>
+      </c>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -28267,56 +28171,56 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>502671</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Paul Goldschmidt</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-08T19:05:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -28330,58 +28234,62 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>36</v>
+        <v>43.8</v>
       </c>
       <c r="Q100" t="n">
-        <v>21</v>
+        <v>54.8</v>
       </c>
       <c r="R100" t="n">
-        <v>82.7</v>
+        <v>23.2</v>
       </c>
       <c r="S100" t="n">
-        <v>93.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T100" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC100" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28401,12 +28309,12 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -28416,12 +28324,12 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/13, 0 HR</t>
+          <t>Last 7 games: 0/20, 0 HR</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 8.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
@@ -28431,112 +28339,104 @@
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>99.3313</t>
+          <t>100.7558</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.4094</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>0.1777</t>
+          <t>0.1944</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>0.3115</t>
+          <t>0.3225</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>71.88</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>0.1822</t>
+          <t>0.1868</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4716</t>
         </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
-          <t>0.1087</t>
+          <t>0.2009</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>26.53</t>
-        </is>
-      </c>
-      <c r="BG100" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH100" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t>29.88</t>
+        </is>
+      </c>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
       <c r="BI100" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ100" t="inlineStr"/>
@@ -28547,32 +28447,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>656555</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Rhys Hoskins</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -28582,17 +28482,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -28614,22 +28514,22 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>43.8</v>
+        <v>42</v>
       </c>
       <c r="Q101" t="n">
-        <v>54.8</v>
+        <v>39</v>
       </c>
       <c r="R101" t="n">
-        <v>23.2</v>
+        <v>39.1</v>
       </c>
       <c r="S101" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T101" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>34.9</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -28668,7 +28568,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr"/>
@@ -28685,27 +28585,27 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/20, 0 HR</t>
+          <t>Last 7 games: 3/13, 1 HR</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
@@ -28715,104 +28615,112 @@
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>100.7558</t>
+          <t>99.9272</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>0.4094</t>
+          <t>0.3554</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>0.1944</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>0.3225</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>71.88</t>
+          <t>71.63</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.08</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>0.1868</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>0.4716</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
-          <t>0.2009</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>29.88</t>
-        </is>
-      </c>
-      <c r="BG101" t="inlineStr"/>
-      <c r="BH101" t="inlineStr"/>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH101" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI101" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ101" t="inlineStr"/>
@@ -28823,22 +28731,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>656555</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Rhys Hoskins</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -28853,26 +28761,26 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -28886,62 +28794,58 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>42</v>
+        <v>44.4</v>
       </c>
       <c r="Q102" t="n">
-        <v>39</v>
+        <v>32.8</v>
       </c>
       <c r="R102" t="n">
-        <v>39.1</v>
+        <v>49.6</v>
       </c>
       <c r="S102" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T102" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U102" t="n">
-        <v>34.9</v>
+        <v>28.2</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -28961,132 +28865,132 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 1 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>99.9272</t>
+          <t>101.3257</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.3554</t>
+          <t>0.4355</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.1697</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>71.63</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.1947</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH102" t="inlineStr">
@@ -29096,7 +29000,7 @@
       </c>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -29107,27 +29011,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>655316</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T20:10:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -29137,26 +29041,26 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -29170,26 +29074,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>44.4</v>
+        <v>29.3</v>
       </c>
       <c r="Q103" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="R103" t="n">
-        <v>49.6</v>
+        <v>72.2</v>
       </c>
       <c r="S103" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U103" t="n">
-        <v>28.2</v>
+        <v>35.6</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29198,34 +29102,30 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -29245,12 +29145,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29260,127 +29160,127 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.5% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>101.3257</t>
+          <t>98.0297</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.4355</t>
+          <t>0.3917</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.3045</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.17</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>42.79</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1947</t>
+          <t>0.1824</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -29391,52 +29291,52 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>655316</t>
+          <t>677951</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Bobby Witt</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-08T20:10:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -29454,61 +29354,65 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>29.3</v>
+        <v>58.1</v>
       </c>
       <c r="Q104" t="n">
-        <v>32.3</v>
+        <v>30.9</v>
       </c>
       <c r="R104" t="n">
-        <v>72.2</v>
+        <v>23.2</v>
       </c>
       <c r="S104" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T104" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U104" t="n">
-        <v>35.6</v>
+        <v>24</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr"/>
@@ -29525,12 +29429,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29540,127 +29444,119 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.5% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.8% barrel, 6.3 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>92.95</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>98.0297</t>
+          <t>103.6779</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3917</t>
+          <t>0.5143</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3045</t>
+          <t>0.3797</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>69.17</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1824</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.49</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3744</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BG104" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH104" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t>20.86</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29671,47 +29567,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>677951</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-08T19:05:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>605280</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29720,7 +29616,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29734,65 +29630,61 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>58.1</v>
+        <v>17</v>
       </c>
       <c r="Q105" t="n">
-        <v>30.9</v>
+        <v>45.1</v>
       </c>
       <c r="R105" t="n">
-        <v>23.2</v>
+        <v>82.7</v>
       </c>
       <c r="S105" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T105" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U105" t="n">
-        <v>24</v>
+        <v>25.3</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29809,134 +29701,142 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 3/18, 1 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.8% barrel, 6.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>92.95</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>103.6779</t>
+          <t>96.7879</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.5143</t>
+          <t>0.3625</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3797</t>
+          <t>0.2892</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>68.93</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.1593</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.3744</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>20.86</t>
-        </is>
-      </c>
-      <c r="BG105" t="inlineStr"/>
-      <c r="BH105" t="inlineStr"/>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -32558,34 +32458,30 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -33394,34 +33290,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -34246,34 +34138,30 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36766,34 +36654,30 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39856,28 +39740,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -40410,34 +40298,30 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -40694,34 +40578,30 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42378,34 +42258,30 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43218,34 +43094,30 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44906,34 +44778,30 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -47690,34 +47558,30 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB169" t="inlineStr"/>
       <c r="AC169" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -49378,34 +49242,30 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49571,47 +49431,47 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T19:05:00Z</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -49634,26 +49494,26 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>34.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q176" t="n">
-        <v>32.8</v>
+        <v>46.3</v>
       </c>
       <c r="R176" t="n">
-        <v>49.6</v>
+        <v>82.7</v>
       </c>
       <c r="S176" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T176" t="n">
         <v>80</v>
       </c>
       <c r="U176" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -49662,37 +49522,33 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr"/>
@@ -49709,12 +49565,12 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
@@ -49724,12 +49580,12 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 4/18, 0 HR</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -49739,112 +49595,112 @@
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>99.7265</t>
+          <t>98.2348</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>0.4047</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.3246</t>
+          <t>0.272</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>74.52</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>48.02</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH176" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI176" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ176" t="inlineStr"/>
@@ -49855,27 +49711,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-08T22:05:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -49885,17 +49741,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -49904,7 +49760,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -49918,65 +49774,61 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>7.4</v>
+        <v>34.3</v>
       </c>
       <c r="Q177" t="n">
-        <v>50.6</v>
+        <v>32.8</v>
       </c>
       <c r="R177" t="n">
-        <v>80.3</v>
+        <v>49.6</v>
       </c>
       <c r="S177" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T177" t="n">
         <v>80</v>
       </c>
       <c r="U177" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr"/>
@@ -49993,142 +49845,142 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 25.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>95.8799</t>
+          <t>99.7265</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.4047</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.0971</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.3246</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>48.02</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>88.91</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>0.4268</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH177" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>
@@ -50139,47 +49991,47 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-08T19:05:00Z</t>
+          <t>2026-08-08T22:05:00Z</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -50188,7 +50040,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -50202,61 +50054,65 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>15.4</v>
+        <v>7.4</v>
       </c>
       <c r="Q178" t="n">
-        <v>46.3</v>
+        <v>50.6</v>
       </c>
       <c r="R178" t="n">
-        <v>82.7</v>
+        <v>80.3</v>
       </c>
       <c r="S178" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T178" t="n">
         <v>80</v>
       </c>
       <c r="U178" t="n">
-        <v>12</v>
+        <v>43.2</v>
       </c>
       <c r="V178" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W178" t="inlineStr">
+      <c r="Z178" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr"/>
@@ -50273,127 +50129,127 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 25.0 HR allowed</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>98.2348</t>
+          <t>95.8799</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.0971</t>
         </is>
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.91</t>
         </is>
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.4268</t>
         </is>
       </c>
       <c r="BE178" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr">
@@ -50403,12 +50259,12 @@
       </c>
       <c r="BH178" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI178" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ178" t="inlineStr"/>
@@ -54130,34 +53986,30 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -56658,34 +56510,30 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57498,34 +57346,30 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -58898,34 +58742,30 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -60022,34 +59862,30 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB213" t="inlineStr"/>
       <c r="AC213" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -61710,34 +61546,30 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB219" t="inlineStr"/>
       <c r="AC219" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -61994,34 +61826,30 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB220" t="inlineStr"/>
       <c r="AC220" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -62278,34 +62106,30 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB221" t="inlineStr"/>
       <c r="AC221" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -65622,34 +65446,30 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB233" t="inlineStr"/>
       <c r="AC233" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -66186,34 +66006,30 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB235" t="inlineStr"/>
       <c r="AC235" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70086,34 +69902,30 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB249" t="inlineStr"/>
       <c r="AC249" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70368,28 +70180,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W250" t="inlineStr"/>
-      <c r="X250" t="inlineStr"/>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y250" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB250" t="inlineStr"/>
       <c r="AC250" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70646,34 +70462,30 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB251" t="inlineStr"/>
       <c r="AC251" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -74278,34 +74090,30 @@
       </c>
       <c r="W264" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB264" t="inlineStr"/>
       <c r="AC264" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74562,34 +74370,30 @@
       </c>
       <c r="W265" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB265" t="inlineStr"/>
       <c r="AC265" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75122,34 +74926,30 @@
       </c>
       <c r="W267" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB267" t="inlineStr"/>
       <c r="AC267" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77404,34 +77204,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -77688,34 +77484,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -77972,34 +77764,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -79104,34 +78892,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -79668,34 +79452,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -80701,47 +80481,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>682848</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Endy Rodríguez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-08T19:05:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -80750,7 +80530,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -80764,26 +80544,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>48.7</v>
+        <v>39.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>82.7</v>
+        <v>67.8</v>
       </c>
       <c r="S16" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>48.3</v>
+        <v>62.4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -80797,7 +80577,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -80818,7 +80598,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -80835,142 +80615,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>46.17</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>90.76</t>
+          <t>92.34</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.4691</t>
+          <t>100.3363</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4786</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1921</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3416</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>46.21</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>33.36</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1922</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -80981,27 +80761,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>682848</t>
+          <t>646240</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Endy Rodríguez</t>
+          <t>Rafael Devers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -81011,17 +80791,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -81030,7 +80810,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -81044,26 +80824,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>39.9</v>
+        <v>58.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>75.09999999999999</v>
+        <v>47.4</v>
       </c>
       <c r="R17" t="n">
-        <v>67.8</v>
+        <v>53.3</v>
       </c>
       <c r="S17" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>62.4</v>
+        <v>56.2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -81072,37 +80852,33 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -81119,7 +80895,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -81139,122 +80915,122 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>12.64</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.17</t>
+          <t>52.74</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>92.34</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.3363</t>
+          <t>103.133</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.2231</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.2291</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -81265,27 +81041,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>646240</t>
+          <t>701398</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rafael Devers</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T22:45:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -81295,26 +81071,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jackson Jobe</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>61.8</v>
+        <v>61.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -81328,26 +81104,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>58.1</v>
+        <v>61.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>47.4</v>
+        <v>22</v>
       </c>
       <c r="R18" t="n">
-        <v>53.3</v>
+        <v>71.7</v>
       </c>
       <c r="S18" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>56.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -81361,7 +81137,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -81382,7 +81158,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -81399,142 +81175,142 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.4% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>52.74</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>103.133</t>
+          <t>101.6267</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.5201</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.2231</t>
+          <t>0.2589</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.2291</t>
+          <t>0.2438</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>0.3486</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1025</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -81545,56 +81321,56 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>701398</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-08T22:45:00Z</t>
+          <t>2026-08-08T19:05:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -81608,26 +81384,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>61.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>46.3</v>
       </c>
       <c r="R19" t="n">
-        <v>71.7</v>
+        <v>82.7</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>77.40000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -81641,7 +81417,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -81662,7 +81438,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -81679,127 +81455,127 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.4% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>90.76</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.6267</t>
+          <t>103.4691</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.5201</t>
+          <t>0.4786</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2589</t>
+          <t>0.1921</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.3416</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2438</t>
+          <t>0.1922</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3486</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1025</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -81814,7 +81590,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08.xlsx
@@ -1575,27 +1575,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>664040</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-09T00:10:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1638,26 +1638,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>81.2</v>
+        <v>52.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.9</v>
+        <v>75.2</v>
       </c>
       <c r="R5" t="n">
-        <v>41.7</v>
+        <v>68.8</v>
       </c>
       <c r="S5" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>94.7</v>
+        <v>32.5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1709,142 +1709,142 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.57</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>93.85</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>104.4492</t>
+          <t>101.4635</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.3078</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>52.59</t>
+          <t>40.37</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1666</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -1855,27 +1855,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>664040</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-09T00:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>52.8</v>
+        <v>81.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.2</v>
+        <v>43.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.8</v>
+        <v>41.7</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>32.5</v>
+        <v>94.7</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1989,142 +1989,142 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>54.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>93.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.4635</t>
+          <t>104.4492</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.3078</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.73</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>52.59</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.1666</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>75.2</v>
       </c>
       <c r="R9" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S11" t="n">
         <v>96.59999999999999</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8299,27 +8299,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>673548</t>
+          <t>687462</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8362,26 +8362,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>46.3</v>
+        <v>25.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>56.8</v>
+        <v>75.2</v>
       </c>
       <c r="R29" t="n">
-        <v>52.7</v>
+        <v>68.8</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U29" t="n">
-        <v>44.8</v>
+        <v>3.4</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8433,142 +8433,142 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>33.83</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.1779</t>
+          <t>97.6733</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4426</t>
+          <t>0.3881</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1949</t>
+          <t>0.1507</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3394</t>
+          <t>0.3288</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4716</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.2009</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8579,27 +8579,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>687462</t>
+          <t>673548</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8642,26 +8642,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>25.9</v>
+        <v>46.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>75.2</v>
+        <v>56.8</v>
       </c>
       <c r="R30" t="n">
-        <v>67.8</v>
+        <v>52.7</v>
       </c>
       <c r="S30" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>3.4</v>
+        <v>44.8</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8713,142 +8713,142 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 8/27, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>33.83</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>97.6733</t>
+          <t>101.1779</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.3881</t>
+          <t>0.4426</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1507</t>
+          <t>0.1949</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3288</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.4716</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.2009</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>33.7</v>
       </c>
       <c r="R34" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S34" t="n">
         <v>100</v>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14183,27 +14183,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>676724</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14213,17 +14213,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14246,26 +14246,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>43.8</v>
+        <v>43.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>54.8</v>
+        <v>34.5</v>
       </c>
       <c r="R50" t="n">
-        <v>52.7</v>
+        <v>68.8</v>
       </c>
       <c r="S50" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T50" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14317,27 +14317,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14347,112 +14347,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>100.7558</t>
+          <t>101.4586</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4094</t>
+          <t>0.4252</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1944</t>
+          <t>0.1913</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3225</t>
+          <t>0.3219</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>71.88</t>
+          <t>73.37</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1868</t>
+          <t>0.2117</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>38.32</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4716</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.2009</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14463,27 +14463,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>676724</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -14493,17 +14493,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14512,7 +14512,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14526,26 +14526,26 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>34.5</v>
+        <v>54.8</v>
       </c>
       <c r="R51" t="n">
-        <v>67.8</v>
+        <v>52.7</v>
       </c>
       <c r="S51" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T51" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U51" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -14597,12 +14597,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 0/20, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14627,112 +14627,112 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>101.4586</t>
+          <t>100.7558</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.4252</t>
+          <t>0.4094</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.1913</t>
+          <t>0.1944</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.3219</t>
+          <t>0.3225</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>73.37</t>
+          <t>71.88</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.2117</t>
+          <t>0.1868</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.4716</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2009</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -17819,27 +17819,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>694378</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Jacob Gonzalez</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17849,17 +17849,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17882,26 +17882,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>48.6</v>
+        <v>25.2</v>
       </c>
       <c r="Q63" t="n">
-        <v>48</v>
+        <v>75.2</v>
       </c>
       <c r="R63" t="n">
-        <v>41.1</v>
+        <v>68.8</v>
       </c>
       <c r="S63" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T63" t="n">
         <v>80</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>35.6</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17936,7 +17936,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -17953,142 +17953,142 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 17.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>103.5486</t>
+          <t>99.3008</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4138</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1391</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.3889</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1582</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18099,27 +18099,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18166,13 +18166,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>47.6</v>
+        <v>48.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>32.8</v>
+        <v>48</v>
       </c>
       <c r="R64" t="n">
-        <v>49.6</v>
+        <v>41.1</v>
       </c>
       <c r="S64" t="n">
         <v>86.40000000000001</v>
@@ -18181,7 +18181,7 @@
         <v>80</v>
       </c>
       <c r="U64" t="n">
-        <v>53.9</v>
+        <v>0</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -18233,142 +18233,142 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>92.15</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>100.4739</t>
+          <t>103.5486</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.4578</t>
+          <t>0.4138</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.2025</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3288</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1685</t>
+          <t>0.1391</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.3889</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1582</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18379,27 +18379,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>694378</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jacob Gonzalez</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -18409,17 +18409,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18428,7 +18428,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18442,26 +18442,26 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>25.2</v>
+        <v>47.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>75.2</v>
+        <v>32.8</v>
       </c>
       <c r="R65" t="n">
-        <v>67.8</v>
+        <v>49.6</v>
       </c>
       <c r="S65" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T65" t="n">
         <v>80</v>
       </c>
       <c r="U65" t="n">
-        <v>35.6</v>
+        <v>53.9</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -18496,7 +18496,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -18513,12 +18513,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18528,12 +18528,12 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -18543,112 +18543,112 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>99.3008</t>
+          <t>100.4739</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.4578</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.2025</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3288</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1685</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -20619,27 +20619,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>670231</t>
+          <t>680779</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>John Rave</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20649,17 +20649,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>605280</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20682,26 +20682,26 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Pitcher Vulnerable</t>
         </is>
       </c>
       <c r="P73" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="R73" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="S73" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T73" t="n">
         <v>50</v>
       </c>
-      <c r="Q73" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="R73" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="S73" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="T73" t="n">
-        <v>80</v>
-      </c>
       <c r="U73" t="n">
-        <v>33.7</v>
+        <v>4.5</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20753,142 +20753,142 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 1 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.8% barrel, 6.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>101.1154</t>
+          <t>100.639</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.4638</t>
+          <t>0.3589</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.2137</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>43.26</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>48.93</t>
+          <t>50.51</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.26</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.2489</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.3744</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20899,27 +20899,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>680779</t>
+          <t>670231</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>John Rave</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20929,17 +20929,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -20948,7 +20948,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20962,54 +20962,58 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>36.6</v>
+        <v>50</v>
       </c>
       <c r="Q74" t="n">
-        <v>75.2</v>
+        <v>30.9</v>
       </c>
       <c r="R74" t="n">
-        <v>67.8</v>
+        <v>52.7</v>
       </c>
       <c r="S74" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U74" t="n">
-        <v>4.5</v>
+        <v>33.7</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21029,142 +21033,142 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 4/18, 1 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.8% barrel, 6.3 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>39.09</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>100.639</t>
+          <t>101.1154</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.3589</t>
+          <t>0.4638</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.2137</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.344</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>50.51</t>
+          <t>48.93</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.2489</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>43.49</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.3744</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -21735,27 +21739,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>683002</t>
+          <t>805999</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>A.J. Ewing</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -21770,12 +21774,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21784,7 +21788,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21802,13 +21806,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>37.7</v>
+        <v>33.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>49.3</v>
+        <v>34.5</v>
       </c>
       <c r="R77" t="n">
-        <v>41.1</v>
+        <v>68.8</v>
       </c>
       <c r="S77" t="n">
         <v>93.2</v>
@@ -21817,7 +21821,7 @@
         <v>80</v>
       </c>
       <c r="U77" t="n">
-        <v>7</v>
+        <v>23.4</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21852,7 +21856,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21869,12 +21873,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21884,12 +21888,12 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 19.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21899,112 +21903,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>101.4067</t>
+          <t>100.4949</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.1504</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>44.14</t>
+          <t>38.32</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>90.45</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3959</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1651</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22015,27 +22019,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-09T01:50:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -22045,17 +22049,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22078,26 +22082,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>42.9</v>
+        <v>34.5</v>
       </c>
       <c r="R78" t="n">
-        <v>49.9</v>
+        <v>68.8</v>
       </c>
       <c r="S78" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T78" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U78" t="n">
-        <v>40.7</v>
+        <v>26.8</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22111,7 +22115,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22149,12 +22153,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22164,12 +22168,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 11.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22179,112 +22183,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>42.14</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>91.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>101.0841</t>
+          <t>101.4112</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.4212</t>
+          <t>0.4017</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>75.01</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>53.09</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>38.32</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1555</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22295,24 +22299,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>805999</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A.J. Ewing</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>NYM</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>2026-08-08T22:40:00Z</t>
@@ -22325,17 +22329,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22344,7 +22348,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22358,26 +22362,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>33.5</v>
+        <v>16.6</v>
       </c>
       <c r="Q79" t="n">
-        <v>34.5</v>
+        <v>75.2</v>
       </c>
       <c r="R79" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S79" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U79" t="n">
-        <v>23.4</v>
+        <v>10.8</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22391,7 +22395,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22412,7 +22416,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22429,12 +22433,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22444,112 +22448,112 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.05</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>100.4949</t>
+          <t>98.3008</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.3813</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1077</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>12.73</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.0943</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
@@ -22559,7 +22563,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
@@ -22575,27 +22579,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>683002</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -22605,17 +22609,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -22624,7 +22628,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -22638,26 +22642,26 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>40.1</v>
+        <v>37.7</v>
       </c>
       <c r="Q80" t="n">
-        <v>34.5</v>
+        <v>49.3</v>
       </c>
       <c r="R80" t="n">
-        <v>67.8</v>
+        <v>41.1</v>
       </c>
       <c r="S80" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T80" t="n">
         <v>80</v>
       </c>
       <c r="U80" t="n">
-        <v>26.8</v>
+        <v>7</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -22671,7 +22675,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -22714,22 +22718,22 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -22739,112 +22743,112 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>42.14</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>101.4112</t>
+          <t>101.4067</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.4017</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1504</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>75.01</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>53.09</t>
+          <t>47.03</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.171</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>44.14</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.45</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3959</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.1651</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22855,27 +22859,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-08T23:10:00Z</t>
+          <t>2026-08-09T01:50:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -22885,26 +22889,26 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22918,26 +22922,26 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>41.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q81" t="n">
-        <v>35.6</v>
+        <v>42.9</v>
       </c>
       <c r="R81" t="n">
-        <v>41.1</v>
+        <v>49.9</v>
       </c>
       <c r="S81" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T81" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U81" t="n">
-        <v>29.2</v>
+        <v>40.7</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22951,7 +22955,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22989,7 +22993,7 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
@@ -23004,12 +23008,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -23019,112 +23023,112 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>91.16</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>101.0048</t>
+          <t>101.0841</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.4212</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.3537</t>
+          <t>0.3438</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>33.42</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1954</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.3897</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1555</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -23135,27 +23139,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:10:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -23165,26 +23169,26 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23198,26 +23202,26 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>16.6</v>
+        <v>41.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>75.2</v>
+        <v>35.6</v>
       </c>
       <c r="R82" t="n">
-        <v>67.8</v>
+        <v>41.1</v>
       </c>
       <c r="S82" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T82" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U82" t="n">
-        <v>10.8</v>
+        <v>29.2</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -23231,7 +23235,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -23279,132 +23283,132 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>87.05</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>98.3008</t>
+          <t>101.0048</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3813</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.1077</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.3537</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.86</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>34.86</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.0943</t>
+          <t>0.1954</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>35.79</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.3897</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>27.17</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -23415,27 +23419,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>642715</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -23445,17 +23449,17 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Jackson Jobe</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -23478,26 +23482,26 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>37.9</v>
+        <v>6.2</v>
       </c>
       <c r="Q83" t="n">
-        <v>47.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="R83" t="n">
-        <v>53.3</v>
+        <v>68.8</v>
       </c>
       <c r="S83" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T83" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U83" t="n">
-        <v>18.3</v>
+        <v>12</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -23511,7 +23515,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -23532,7 +23536,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -23549,7 +23553,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
@@ -23559,132 +23563,132 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>99.0916</t>
+          <t>96.7098</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.3965</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.1781</t>
+          <t>0.0752</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.3004</t>
+          <t>0.2837</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>72.21</t>
+          <t>67.51</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>14.86</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.1939</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23695,27 +23699,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>642715</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -23725,17 +23729,17 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -23744,7 +23748,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -23758,26 +23762,26 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>6.2</v>
+        <v>37.9</v>
       </c>
       <c r="Q84" t="n">
-        <v>75.09999999999999</v>
+        <v>47.4</v>
       </c>
       <c r="R84" t="n">
-        <v>67.8</v>
+        <v>53.3</v>
       </c>
       <c r="S84" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T84" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U84" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -23791,7 +23795,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -23812,7 +23816,7 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr"/>
@@ -23829,7 +23833,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
@@ -23839,132 +23843,132 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>96.7098</t>
+          <t>99.0916</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3965</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.0752</t>
+          <t>0.1781</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.2837</t>
+          <t>0.3004</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>67.51</t>
+          <t>72.21</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>34.48</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>0.1939</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>0.438</t>
+        </is>
+      </c>
+      <c r="BE84" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="BF84" t="inlineStr">
+        <is>
           <t>28.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>14.86</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>0.0741</t>
-        </is>
-      </c>
-      <c r="BA84" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
-      </c>
-      <c r="BB84" t="inlineStr">
-        <is>
-          <t>45.03</t>
-        </is>
-      </c>
-      <c r="BC84" t="inlineStr">
-        <is>
-          <t>89.33</t>
-        </is>
-      </c>
-      <c r="BD84" t="inlineStr">
-        <is>
-          <t>0.6059</t>
-        </is>
-      </c>
-      <c r="BE84" t="inlineStr">
-        <is>
-          <t>0.2936</t>
-        </is>
-      </c>
-      <c r="BF84" t="inlineStr">
-        <is>
-          <t>36.99</t>
-        </is>
-      </c>
       <c r="BG84" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -23975,27 +23979,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>682927</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Ronny Simon</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -24005,17 +24009,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -24038,26 +24042,26 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Pitcher Vulnerable, Platoon Edge</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>43.1</v>
+        <v>12.1</v>
       </c>
       <c r="Q85" t="n">
-        <v>41.4</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="R85" t="n">
-        <v>49.6</v>
+        <v>68.8</v>
       </c>
       <c r="S85" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T85" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U85" t="n">
-        <v>46.9</v>
+        <v>15.3</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -24071,7 +24075,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -24104,147 +24108,147 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 3 games: 2/9, 0 HR</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 13.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>101.6455</t>
+          <t>94.2085</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1023</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.3531</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>71.59</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>22.88</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>0.2089</t>
+          <t>0.0117</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>34.74</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI85" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ85" t="inlineStr"/>
@@ -24255,27 +24259,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-09T01:50:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -24285,17 +24289,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -24318,26 +24322,26 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>54.6</v>
+        <v>43.1</v>
       </c>
       <c r="Q86" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="R86" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="S86" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U86" t="n">
-        <v>19.1</v>
+        <v>46.9</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24351,7 +24355,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24389,12 +24393,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -24404,112 +24408,112 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 1 HR</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>100.6066</t>
+          <t>101.6455</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4245</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.2299</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3084</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>53.09</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>53.73</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.2089</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>34.74</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.59</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1555</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr">
@@ -24519,12 +24523,12 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -24535,27 +24539,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>682927</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ronny Simon</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-09T01:50:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24565,17 +24569,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24584,7 +24588,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24598,26 +24602,26 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>12.1</v>
+        <v>54.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>75.09999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="R87" t="n">
-        <v>67.8</v>
+        <v>49.9</v>
       </c>
       <c r="S87" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T87" t="n">
         <v>75</v>
       </c>
       <c r="U87" t="n">
-        <v>15.3</v>
+        <v>19.1</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24631,7 +24635,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24641,7 +24645,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -24649,11 +24653,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24668,147 +24668,147 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 3 games: 2/9, 0 HR</t>
+          <t>Last 7 games: 3/24, 1 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>94.2085</t>
+          <t>100.6066</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.4245</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1023</t>
+          <t>0.2299</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.3531</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>22.88</t>
+          <t>53.09</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>53.73</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>41.59</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.0117</t>
+          <t>0.2041</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.1555</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>34.5</v>
       </c>
       <c r="R103" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S103" t="n">
         <v>96.59999999999999</v>
@@ -29291,7 +29291,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
@@ -29307,27 +29307,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>682626</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-08T23:15:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -29342,17 +29342,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L104" t="n">
@@ -29370,26 +29370,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>56.7</v>
+        <v>56.9</v>
       </c>
       <c r="Q104" t="n">
-        <v>37.5</v>
+        <v>34.5</v>
       </c>
       <c r="R104" t="n">
-        <v>39.1</v>
+        <v>68.8</v>
       </c>
       <c r="S104" t="n">
         <v>44.8</v>
       </c>
       <c r="T104" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U104" t="n">
-        <v>39.7</v>
+        <v>8.1</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr"/>
@@ -29436,17 +29436,17 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29456,12 +29456,12 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 5/13 over last 3 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.6% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29471,112 +29471,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>101.2887</t>
+          <t>102.7776</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>0.4545</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.2164</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.3386</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.31</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>38.32</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29587,27 +29587,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-09T00:10:00Z</t>
+          <t>2026-08-08T23:15:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -29617,22 +29617,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L105" t="n">
@@ -29650,57 +29650,61 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>49.1</v>
+        <v>56.7</v>
       </c>
       <c r="Q105" t="n">
-        <v>25.2</v>
+        <v>37.5</v>
       </c>
       <c r="R105" t="n">
-        <v>41.7</v>
+        <v>39.1</v>
       </c>
       <c r="S105" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T105" t="n">
         <v>75</v>
       </c>
       <c r="U105" t="n">
-        <v>0.8</v>
+        <v>39.7</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y105" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29712,17 +29716,17 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -29732,12 +29736,12 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Contact streak: 5/13 over last 3 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 14.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.6% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29747,112 +29751,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>90.45</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>102.3357</t>
+          <t>101.2887</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.4857</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3592</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.2032</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1235</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -29863,27 +29867,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>682626</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-09T00:10:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -29893,17 +29897,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Bubba Chandler</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>696149</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -29912,7 +29916,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29926,50 +29930,42 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>56.9</v>
+        <v>49.1</v>
       </c>
       <c r="Q106" t="n">
-        <v>34.5</v>
+        <v>25.2</v>
       </c>
       <c r="R106" t="n">
-        <v>67.8</v>
+        <v>41.7</v>
       </c>
       <c r="S106" t="n">
-        <v>44.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U106" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -29977,7 +29973,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29997,12 +29997,12 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -30012,12 +30012,12 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 7.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -30027,112 +30027,112 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.45</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>102.7776</t>
+          <t>102.3357</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.4545</t>
+          <t>0.4857</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.2164</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.3386</t>
+          <t>0.3592</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>27.71</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.2032</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>36.48</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.1235</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -39148,7 +39148,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>34.5</v>
       </c>
       <c r="R139" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S139" t="n">
         <v>86.40000000000001</v>
@@ -39363,7 +39363,7 @@
       </c>
       <c r="BH139" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI139" t="inlineStr">
@@ -43628,7 +43628,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>34.5</v>
       </c>
       <c r="R155" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S155" t="n">
         <v>64.3</v>
@@ -43843,7 +43843,7 @@
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
@@ -50340,7 +50340,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>33.7</v>
       </c>
       <c r="R179" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S179" t="n">
         <v>52.4</v>
@@ -50555,7 +50555,7 @@
       </c>
       <c r="BH179" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI179" t="inlineStr">
@@ -62381,27 +62381,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>664040</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Brandon Lowe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-09T00:10:00Z</t>
+          <t>2026-08-08T22:40:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -62411,17 +62411,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -62444,26 +62444,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>81.2</v>
+        <v>52.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.9</v>
+        <v>75.2</v>
       </c>
       <c r="R5" t="n">
-        <v>41.7</v>
+        <v>68.8</v>
       </c>
       <c r="S5" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>94.7</v>
+        <v>32.5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -62477,7 +62477,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -62515,142 +62515,142 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.57</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>93.85</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>104.4492</t>
+          <t>101.4635</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.3078</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>52.59</t>
+          <t>40.37</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.6059</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1666</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -62661,27 +62661,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>664040</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brandon Lowe</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-08T22:40:00Z</t>
+          <t>2026-08-09T00:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -62691,17 +62691,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -62710,7 +62710,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -62724,26 +62724,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Pitcher Vulnerable, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>52.8</v>
+        <v>81.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.2</v>
+        <v>43.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.8</v>
+        <v>41.7</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>32.5</v>
+        <v>94.7</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -62795,142 +62795,142 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.0% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>54.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>93.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.4635</t>
+          <t>104.4492</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.3078</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.73</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>52.59</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.6059</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.1666</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -63550,7 +63550,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>75.2</v>
       </c>
       <c r="R9" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -63765,7 +63765,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -64110,7 +64110,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="S11" t="n">
         <v>96.59999999999999</v>
@@ -64325,7 +64325,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
